--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>195 000 € 7 500 €/m² Paris 20 Murs de Boutique de 26 m2 libre de toute ... 1 pièce · 26 m² Télégraphe-Pelleport Saint Fargeau, Paris 20ème arrondissement (75020) Voir l'annonce</t>
+          <t>1 nouvelle annonce dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 190 000 € Local commercial 25 m² Paris 20ème arrondissement (75020) CAPITAL TRANSACTION Voir l'annonce Se désinscrire | Nous contacter Cet e-mail vous a été envoyé sur georgesdurand75+lesmurs@gmail.com parce que vous avez souscrit à une alerte s</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-d299d7aa.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_sous_objectif</t>
+          <t>loyer_estime · rendement_sous_objectif · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
